--- a/main/ig/StructureDefinition-fr-lm-location.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-location.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-location.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-location.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-location.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-location.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-location.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-location.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-location.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="101">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>Type de fonction exercée sur le lieu</t>
+  </si>
+  <si>
+    <t>preferred</t>
   </si>
   <si>
     <t>(preferred): https://terminology.hl7.org/ValueSet-v3-ServiceDeliveryLocationRoleType.html</t>
@@ -1232,10 +1235,10 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z6" t="s" s="2">
         <v>73</v>
@@ -1273,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1299,13 +1302,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1356,7 +1359,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1373,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1399,13 +1402,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1456,7 +1459,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1473,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1499,13 +1502,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1556,7 +1559,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
